--- a/docs/PRAP_Programming_Specification_v0.2.xlsx
+++ b/docs/PRAP_Programming_Specification_v0.2.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v1.3.xlsx - change against the v1.2 baseline, awaiting approval</t>
+          <t>PRAP_Development_Plan_v1.3.xlsx - FINAL, approved by Dan 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Approved baseline, Dan 2026-08-01. 65 requirements, 21 validation rules, 11 decisions.</t>
+          <t>FINAL development plan, approved by Dan 2026-08-01. 65 requirements, 21 validation rules, 11 decisions, source schema version 2.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">

--- a/docs/PRAP_Programming_Specification_v0.2.xlsx
+++ b/docs/PRAP_Programming_Specification_v0.2.xlsx
@@ -2416,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2582,8 +2582,31 @@
       </c>
       <c r="E9" s="15" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>S2-06</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>The dummy dataset now holds 62 projects and 289 assignments, above REQ-NFR-03's headroom figure of 50 projects and 500 assignments. The requirement's working-volume figure (20 projects, 30 people) is well below what the dataset represents.</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Treated as a deliberate stress fixture, not a change to REQ-NFR-03. If 50+ trials is the real working volume rather than an upper bound, the requirement should be re-baselined at Step 4 rather than left understating it.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>None of these blocks Step 3. Each changes a single rule that the application reads as data or applies in one place.</t>
         </is>
@@ -2808,12 +2831,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.2.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.3.xlsx</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Populated dataset exercising every rule.</t>
+          <t>50 clinical trials, 12 'Others' projects, 20 people, 289 assignments over 73 months.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -5385,7 +5408,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>Plus the whole dummy dataset: running tools/verify_source_workbook.py against PRAP_SourceData_Dummy_v1.2.xlsx must give no errors, one V-21 warning on PRJ-002, 38 over-allocated person-months and 14 under-allocation runs. Those numbers are the regression baseline for Step 4.</t>
+          <t>Plus the whole dummy dataset: running tools/verify_source_workbook.py against PRAP_SourceData_Dummy_v1.3.xlsx must give no errors and no warnings, across 62 projects, 20 people, 289 assignments and 308 periods spanning 73 months. Every period set must be contiguous, 30 trials must show two 'Conduct' stretches, and 12 must carry the seventh period. Those figures are the regression baseline for Step 4.</t>
         </is>
       </c>
     </row>
